--- a/output/independent-code-review/claude/sample-2/workpaper.xlsx
+++ b/output/independent-code-review/claude/sample-2/workpaper.xlsx
@@ -1371,7 +1371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:12:13.509632Z</t>
+          <t>2026-07-03T03:32:12.174534Z</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
@@ -1458,13 +1458,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="16" t="n">
-        <v>1407</v>
+        <v>1441</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>0.20565</v>
+        <v>0.2082</v>
       </c>
       <c r="I2" s="16" t="n">
-        <v>20042</v>
+        <v>20593</v>
       </c>
     </row>
     <row r="3">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:12:27.884788Z</t>
+          <t>2026-07-03T03:32:37.674329Z</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
@@ -1493,13 +1493,13 @@
         <v>0</v>
       </c>
       <c r="G3" s="16" t="n">
-        <v>881</v>
+        <v>1903</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>0.176295</v>
+        <v>0.252945</v>
       </c>
       <c r="I3" s="16" t="n">
-        <v>14360</v>
+        <v>25488</v>
       </c>
     </row>
     <row r="4">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:12:50.407995Z</t>
+          <t>2026-07-03T03:33:00.969443Z</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
@@ -1528,13 +1528,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>1515</v>
+        <v>1556</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>0.223125</v>
+        <v>0.2262</v>
       </c>
       <c r="I4" s="16" t="n">
-        <v>22513</v>
+        <v>23287</v>
       </c>
     </row>
     <row r="5">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:13:03.363074Z</t>
+          <t>2026-07-03T03:33:40.675628Z</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>judge:code-review-prior-to-main-merge:sample-1</t>
+          <t>judge:code-review-before-merge-to-main:sample-1</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
@@ -1557,19 +1557,19 @@
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>4675</v>
+        <v>17781</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>2638</v>
+        <v>0</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>945</v>
+        <v>3199</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>0.105387</v>
+        <v>0.50664</v>
       </c>
       <c r="I5" s="16" t="n">
-        <v>12944</v>
+        <v>14174</v>
       </c>
     </row>
     <row r="6">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:13:16.199623Z</t>
+          <t>2026-07-03T03:34:20.967393Z</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -1592,19 +1592,19 @@
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>4648</v>
+        <v>17817</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>2638</v>
+        <v>0</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>998</v>
+        <v>3171</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>0.108957</v>
+        <v>0.50508</v>
       </c>
       <c r="I6" s="16" t="n">
-        <v>12834</v>
+        <v>13992</v>
       </c>
     </row>
     <row r="7">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:13:41.442272Z</t>
+          <t>2026-07-03T03:35:30.646658Z</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>judge:testing-per-policy:sample-1</t>
+          <t>judge:testing-per-testing-policy:sample-1</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
@@ -1627,19 +1627,19 @@
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>6393</v>
+        <v>23199</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>2638</v>
+        <v>0</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>1944</v>
+        <v>5402</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>0.206082</v>
+        <v>0.753135</v>
       </c>
       <c r="I7" s="16" t="n">
-        <v>25240</v>
+        <v>26173</v>
       </c>
     </row>
     <row r="8">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:14:05.324278Z</t>
+          <t>2026-07-03T03:35:54.379157Z</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -1668,179 +1668,39 @@
         <v>0</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>1687</v>
+        <v>1605</v>
       </c>
       <c r="H8" s="19" t="n">
-        <v>0.235485</v>
+        <v>0.229335</v>
       </c>
       <c r="I8" s="16" t="n">
-        <v>23872</v>
+        <v>23722</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:14:29.583419Z</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>7295</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>1754</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.240975</v>
-      </c>
-      <c r="I9" s="16" t="n">
-        <v>24265</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:14:42.378276Z</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-main-merge:sample-2</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>4299</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>1055</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>0.107997</v>
-      </c>
-      <c r="I10" s="16" t="n">
-        <v>12795</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:14:55.046889Z</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-2</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>4272</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>1101</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0.111042</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>12667</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:15:16.003233Z</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-2</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>6017</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>1616</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>0.175842</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>20956</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E13" s="20">
-        <f>SUM(E2:E12)</f>
+      <c r="E9" s="20">
+        <f>SUM(E2:E8)</f>
         <v/>
       </c>
-      <c r="F13" s="20">
-        <f>SUM(F2:F12)</f>
+      <c r="F9" s="20">
+        <f>SUM(F2:F8)</f>
         <v/>
       </c>
-      <c r="G13" s="20">
-        <f>SUM(G2:G12)</f>
+      <c r="G9" s="20">
+        <f>SUM(G2:G8)</f>
         <v/>
       </c>
-      <c r="H13" s="21">
-        <f>SUM(H2:H12)</f>
+      <c r="H9" s="21">
+        <f>SUM(H2:H8)</f>
         <v/>
       </c>
-      <c r="I13" s="20">
-        <f>SUM(I2:I12)</f>
+      <c r="I9" s="20">
+        <f>SUM(I2:I8)</f>
         <v/>
       </c>
     </row>

--- a/output/independent-code-review/claude/sample-2/workpaper.xlsx
+++ b/output/independent-code-review/claude/sample-2/workpaper.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 03:15 UTC</t>
+          <t>03 Jul 2026, 03:51 UTC</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Provide additional evidence to close “Testing is performed in accordance with the testing policy”. Specifically: The CI workflow run summary shows overall Success with the matrix build (11 jobs), lint (3 jobs), test debug/release across macOS/Windows/Linux, and bench jobs all completing green, which addresses unit/integration/E2E execution and CI-visible status.</t>
+          <t>Provide additional evidence to close “Testing is performed in accordance with the testing policy”. Specifically: The evidence shows CI ran and completed with Success status, and the PR merged with "33 of 36 checks passed" — but no coverage report is present in the evidence bundle.</t>
         </is>
       </c>
     </row>
@@ -884,11 +884,11 @@
         </is>
       </c>
       <c r="C2" s="16" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>A pull request (#31272) exists for the change and shows a 'Merged' status, evidencing a code review record. dsherret approved the PR 20 hours ago, and the merge into denoland:main occurred 19 hours ago — the approval timestamp precedes the merge timestamp. The change reached main via the PR merge (commit 7ada8d6), not via a direct commit. Note: independence of the reviewer (dsherret vs. author bartlomieju) is a separate attribute; here the criterion is simply that a review occurred before merge, which it did.</t>
+          <t>A pull request (PR #31272) exists for the change and shows an approval by dsherret 20 hours ago, followed by the merge to denoland:main 19 hours ago — approval precedes merge by ~1 hour. The PR footer confirms it was "successfully merged and closed" with merge commit 7ada8d6, indicating the change went to main via the PR rather than by direct commit. Independence of the reviewer is a separate attribute; this attribute only requires that the review occurred before the merge, which the evidence positively demonstrates.</t>
         </is>
       </c>
       <c r="E2" s="16" t="n">
@@ -896,7 +896,8 @@
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>Reviewer independence (author vs. reviewer being distinct humans) is a separate attribute in this control and is not evaluated here; this attribute only requires that a review occurred before merge.</t>
+          <t>Independence of dsherret vs. author bartlomieju is relevant to a separate 'independent reviewer' attribute and is not judged here.
+Copilot AI review noted but not relied upon — this attribute is satisfied by the human approval from dsherret regardless.</t>
         </is>
       </c>
     </row>
@@ -912,11 +913,11 @@
         </is>
       </c>
       <c r="C3" s="16" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>PR #31272 has a recorded approval from dsherret (green check, "approved these changes 20 hours ago"), who is a different human from the author/committer bartlomieju, satisfying the 4-eyes principle. dsherret is labelled 'Member' of the denoland org, indicating authority to approve in the repo, and does not appear as a committer or co-author on the 7 commits (all authored by bartlomieju and Verified). The Copilot AI review is disregarded as it is not an independent human reviewer, but dsherret's approval independently satisfies the criteria.</t>
+          <t>The PR author/committer is bartlomieju and the approving reviewer is dsherret — a different named human — who approved 20 hours ago, before the merge 19 hours ago. Copilot (AI) is also listed as a reviewer but is not relied on for independence; dsherret's human approval satisfies the 4-eyes principle. No indication that dsherret committed or co-authored the 7 commits, all of which are attributed to bartlomieju.</t>
         </is>
       </c>
       <c r="E3" s="16" t="n">
@@ -924,7 +925,7 @@
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>Copilot AI review was considered but rejected as an independent reviewer — bots/AI do not satisfy the human 4-eyes requirement. However, dsherret independently provides the required human approval.</t>
+          <t>Copilot AI 'review' considered and rejected as satisfying independence — bots/AI do not qualify as an independent human reviewer, but dsherret's human approval independently satisfies the criterion.</t>
         </is>
       </c>
     </row>
@@ -940,19 +941,21 @@
         </is>
       </c>
       <c r="C4" s="16" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>The CI workflow run summary shows overall Success with the matrix build (11 jobs), lint (3 jobs), test debug/release across macOS/Windows/Linux, and bench jobs all completing green, which addresses unit/integration/E2E execution and CI-visible status. However, the PR page shows only "33 of 36 checks passed" — 3 checks did not pass and their identity/severity is not visible. In addition, no coverage report is present in evidence (line/branch/function coverage percentages, ≥80%/≥70%/≥80% thresholds), no security scan review artifact is visible, and there is no indication of manual smoke tests. To flip to SUCCESS, evidence needed: (a) identity/status of the 3 non-passing checks (skipped vs failed), (b) a coverage report showing line ≥80%, branch ≥70%, function ≥80% reviewed as part of the PR, and (c) security scan results and their review/approval.</t>
+          <t>The evidence shows CI ran and completed with Success status, and the PR merged with "33 of 36 checks passed" — but no coverage report is present in the evidence bundle. I cannot verify the policy's numeric thresholds (line ≥80%, branch ≥70%, function ≥80%, integration ≥60%). Additionally, "33 of 36 checks passed" implies 3 checks did not pass — the disposition of those 3 (skipped vs failed) is not shown, and the policy requires all unit/integration/E2E tests to pass with zero failures. A coverage report screenshot for this PR and a breakdown of the 3 non-passing checks would resolve this to SUCCESS or FAIL.</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>Considered whether the change qualifies as a documentation-only or refactor exception — rejected: PR modifies runtime timer implementation (switches from Web API timers to Node.js timers, marked BREAKING originally), which is a behavioral code change, not exempt.</t>
+          <t>Documentation-only — rejected: PR modifies runtime timer behavior across 19 files.
+Dependency bump / behavior-preserving refactor — rejected: PR is labeled feat(BREAKING) and changes default timer implementation, a behavioral change.
+Build/deployment scripts — rejected: change is to application logic, not CI/build config.</t>
         </is>
       </c>
     </row>
@@ -967,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1011,12 +1014,12 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>PR header / status badge</t>
+          <t>Reviewers panel / approval event</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>Purple 'Merged' badge on PR #31272; header states 'bartlomieju merged 7 commits into denoland:main from bartlomieju:node_timers 19 hours ago'.</t>
+          <t>'dsherret approved these changes 20 hours ago' with green check icon; Copilot also listed but as AI reviewer.</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1036,12 @@
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>Timeline — approval event</t>
+          <t>Merge event line near footer</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>'dsherret approved these changes 20 hours ago' with green check icon and LGTM comment.</t>
+          <t>'bartlomieju merged commit 7ada8d6 into denoland:main 19 hours ago' — merge occurred 1 hour after the 20-hour-ago approval.</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1058,12 @@
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>Timeline — merge event</t>
+          <t>PR header / status badge</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>'bartlomieju merged commit 7ada8d6 into denoland:main 19 hours ago' — occurred after the 20-hours-ago approval.</t>
+          <t>PR #31272 exists with 'Merged' badge; header states '7 commits into denoland:main from bartlomieju:node_timers', confirming the change reached main via the PR.</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1080,12 @@
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Reviewers panel</t>
+          <t>Footer banner</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>dsherret listed with green approval checkmark; Copilot listed with comment icon (non-approval).</t>
+          <t>'Pull request successfully merged and closed — the branch has been merged.'</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1102,12 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>Timeline / approval event</t>
+          <t>Reviewers panel / approval event</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>'dsherret approved these changes 20 hours ago' with a green check icon; comment 'LGTM' labelled 'Member'.</t>
+          <t>dsherret (Member) shown with green check; timeline shows 'dsherret approved these changes 20 hours ago' with LGTM comment.</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1124,12 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>PR header</t>
+          <t>PR header and commit list</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>'bartlomieju merged 7 commits into denoland:main from bartlomieju:node_timers' — author and committer is bartlomieju, distinct from approver dsherret.</t>
+          <t>Header: 'bartlomieju merged 7 commits into denoland:main from bartlomieju:node_timers 19 hours ago'. All 7 listed commits (3461bd5, 0f39d7d, 762a828, 8866044, 8f0236b, 0dbb629, 12cde71) are attributed to bartlomieju; dsherret does not appear as a committer or co-author.</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1146,12 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>Commits list</t>
+          <t>Merge footer</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>All 7 commits (3461bd5, 0f39d7d, 762a828, 8866044, 8f0236b, 0dbb629, 12cde71) added by bartlomieju and Verified; dsherret does not appear as a committer or co-author.</t>
+          <t>Merge event occurred 19 hours ago, after dsherret's approval 20 hours ago — approval precedes merge.</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1168,12 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Reviewers side panel</t>
+          <t>Reviewers panel — Copilot entry</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>Reviewers panel lists dsherret with a green checkmark (approval); Copilot has a comment icon indicating no explicit approval.</t>
+          <t>Copilot listed as reviewer with comment icon (AI review). Not counted toward human independence; dsherret provides the independent human approval.</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1190,12 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>CI workflow run summary header and jobs sidebar</t>
+          <t>CI workflow run header and jobs list</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>Overall run status 'Success', duration 39m 22s; all test/build/lint jobs across macOS/Windows/Linux debug+release and bench show green checks; publish canary skipped.</t>
+          <t>Workflow 'ci' run #71281 (Latest #2) Status: Success, 39m 22s duration; all matrix build (11), matrix lint (3), and test jobs show green success icons; 4 warnings/1 notice are environmental (pwsh cleanup, macOS runner deprecation) and not test failures. No coverage numbers are visible on this page.</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1212,12 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Merge status area below merge event</t>
+          <t>Merge footer line</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>'33 of 36 checks passed' — 3 checks did not pass; their names and pass/fail/skip status are not visible on this screenshot.</t>
+          <t>Merge event states '33 of 36 checks passed' — indicating 3 of 36 checks did not pass (state — skipped, cancelled, or failed — not disclosed on this screen). Checks tab shows 18 but no per-check pass/fail detail is captured.</t>
         </is>
       </c>
     </row>
@@ -1231,34 +1234,12 @@
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Checks tab counter and Files changed counter</t>
+          <t>PR body and diff indicator</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>Checks tab shows 18; Files changed 19 (+66/-51); no coverage report, security scan summary, or smoke test note is referenced in the conversation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Testing is performed in accordance with the testing policy</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>Screenshot 2025-11-14 at 14-31-38 feat use Node.js timers by default · denoland_deno@12cde71.png</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>Annotations section</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>4 warnings and 1 notice; warnings relate to pwsh Login cleanup and PowerShell module path on macOS, and a macOS-13 deprecation notice — no indication of failing tests, but no coverage or security scan output either.</t>
+          <t>Diff is +66 −51 across 19 files touching timer behavior (setTimeout/setInterval switching to Node.js APIs) — not a documentation-only, dependency-bump, or refactor-only change, so no policy exception clearly applies. No coverage report screenshot or link is visible on the PR page.</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1307,12 @@
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>GitHub Actions workflow run summary · 23 facts extracted · 1 people · 5 ambiguity flag(s)</t>
+          <t>GitHub Actions workflow run summary page · 19 facts extracted · 1 people · 5 ambiguity flag(s)</t>
         </is>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
-          <t>testing-per-policy, testing-per-policy</t>
+          <t>testing-per-policy</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1332,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>GitHub Pull Request page · 27 facts extracted · 4 people · 4 ambiguity flag(s)</t>
+          <t>GitHub Pull Request page · 1 facts extracted · 4 people · 3 ambiguity flag(s)</t>
         </is>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>code-review-prior-to-main-merge, code-review-prior-to-main-merge, code-review-prior-to-main-merge, code-review-prior-to-main-merge, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, testing-per-policy, testing-per-policy</t>
+          <t>code-review-prior-to-merge, code-review-prior-to-merge, code-review-prior-to-merge, code-review-prior-to-merge, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, testing-per-policy, testing-per-policy</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1438,7 +1419,7 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:32:12.174534Z</t>
+          <t>2026-07-03T03:48:14.126718Z</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
@@ -1458,13 +1439,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="16" t="n">
-        <v>1441</v>
+        <v>1787</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>0.2082</v>
+        <v>0.23415</v>
       </c>
       <c r="I2" s="16" t="n">
-        <v>20593</v>
+        <v>25332</v>
       </c>
     </row>
     <row r="3">
@@ -1473,7 +1454,7 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:32:37.674329Z</t>
+          <t>2026-07-03T03:48:39.485414Z</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
@@ -1493,13 +1474,13 @@
         <v>0</v>
       </c>
       <c r="G3" s="16" t="n">
-        <v>1903</v>
+        <v>1988</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>0.252945</v>
+        <v>0.25932</v>
       </c>
       <c r="I3" s="16" t="n">
-        <v>25488</v>
+        <v>25349</v>
       </c>
     </row>
     <row r="4">
@@ -1508,7 +1489,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:33:00.969443Z</t>
+          <t>2026-07-03T03:49:00.506620Z</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
@@ -1528,13 +1509,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>1556</v>
+        <v>1515</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>0.2262</v>
+        <v>0.223125</v>
       </c>
       <c r="I4" s="16" t="n">
-        <v>23287</v>
+        <v>21014</v>
       </c>
     </row>
     <row r="5">
@@ -1543,12 +1524,12 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:33:40.675628Z</t>
+          <t>2026-07-03T03:49:13.305737Z</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>judge:code-review-before-merge-to-main:sample-1</t>
+          <t>judge:code-review-prior-to-merge:sample-1</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
@@ -1557,19 +1538,19 @@
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>17781</v>
+        <v>6270</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0</v>
+        <v>3666</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>3199</v>
+        <v>1005</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>0.50664</v>
+        <v>0.119934</v>
       </c>
       <c r="I5" s="16" t="n">
-        <v>14174</v>
+        <v>12795</v>
       </c>
     </row>
     <row r="6">
@@ -1578,7 +1559,7 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:34:20.967393Z</t>
+          <t>2026-07-03T03:49:26.208418Z</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -1592,19 +1573,19 @@
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>17817</v>
+        <v>6246</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>0</v>
+        <v>3666</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>3171</v>
+        <v>1092</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>0.50508</v>
+        <v>0.126099</v>
       </c>
       <c r="I6" s="16" t="n">
-        <v>13992</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="7">
@@ -1613,12 +1594,12 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:35:30.646658Z</t>
+          <t>2026-07-03T03:49:45.900071Z</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>judge:testing-per-testing-policy:sample-1</t>
+          <t>judge:testing-per-policy:sample-1</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
@@ -1627,19 +1608,19 @@
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>23199</v>
+        <v>8041</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>0</v>
+        <v>3666</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>5402</v>
+        <v>1578</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>0.753135</v>
+        <v>0.189474</v>
       </c>
       <c r="I7" s="16" t="n">
-        <v>26173</v>
+        <v>19689</v>
       </c>
     </row>
     <row r="8">
@@ -1648,7 +1629,7 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:35:54.379157Z</t>
+          <t>2026-07-03T03:50:10.052239Z</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -1668,39 +1649,529 @@
         <v>0</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>1605</v>
+        <v>1616</v>
       </c>
       <c r="H8" s="19" t="n">
-        <v>0.229335</v>
+        <v>0.23016</v>
       </c>
       <c r="I8" s="16" t="n">
-        <v>23722</v>
+        <v>24142</v>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="20" t="inlineStr">
+      <c r="A9" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:50:31.032351Z</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>7295</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>1504</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>0.222225</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>20969</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:50:44.382655Z</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>judge:code-review-prior-to-merge:sample-2</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>4057</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>1067</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0.091389</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>13346</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:50:57.753305Z</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-2</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>4033</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>1108</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0.09410399999999999</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>13368</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:51:17.209066Z</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>judge:testing-per-policy:sample-2</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>5828</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>1487</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>0.149454</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>19453</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:51:31.339364Z</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:kubernetes-pr-checks.png</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>4703</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>945</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>0.14142</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>14122</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:52:34.116483Z</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:kubernetes-pr.png</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>4172</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>4640</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>0.41058</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <v>62769</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:52:46.504782Z</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>judge:code-review-prior-to-merge:sample-3</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>6582</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>1002</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>0.124389</v>
+      </c>
+      <c r="I15" s="16" t="n">
+        <v>12384</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:53:04.324724Z</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-3</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>6558</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>1257</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>0.143154</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>17817</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:53:22.086254Z</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>judge:testing-per-policy:sample-3</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>8353</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>1369</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>0.178479</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>17758</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:53:36.065782Z</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:nextjs-pr-checks.png</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>4702</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>924</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>0.13983</v>
+      </c>
+      <c r="I18" s="16" t="n">
+        <v>13972</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:54:01.769450Z</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:nextjs-pr.png</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>6103</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>1808</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>0.227145</v>
+      </c>
+      <c r="I19" s="16" t="n">
+        <v>25696</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:54:15.073618Z</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>judge:code-review-prior-to-merge:sample-4</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>3730</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>989</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>0.080634</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>13300</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:54:26.858373Z</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-4</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>3706</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>902</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>0.073749</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>11782</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:54:43.961668Z</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>judge:testing-per-policy:sample-4</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>5501</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>3666</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>1265</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>0.127899</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <v>17098</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E9" s="20">
-        <f>SUM(E2:E8)</f>
+      <c r="E23" s="20">
+        <f>SUM(E2:E22)</f>
         <v/>
       </c>
-      <c r="F9" s="20">
-        <f>SUM(F2:F8)</f>
+      <c r="F23" s="20">
+        <f>SUM(F2:F22)</f>
         <v/>
       </c>
-      <c r="G9" s="20">
-        <f>SUM(G2:G8)</f>
+      <c r="G23" s="20">
+        <f>SUM(G2:G22)</f>
         <v/>
       </c>
-      <c r="H9" s="21">
-        <f>SUM(H2:H8)</f>
+      <c r="H23" s="21">
+        <f>SUM(H2:H22)</f>
         <v/>
       </c>
-      <c r="I9" s="20">
-        <f>SUM(I2:I8)</f>
+      <c r="I23" s="20">
+        <f>SUM(I2:I22)</f>
         <v/>
       </c>
     </row>

--- a/output/independent-code-review/claude/sample-2/workpaper.xlsx
+++ b/output/independent-code-review/claude/sample-2/workpaper.xlsx
@@ -11,7 +11,6 @@
     <sheet name="Attribute Verdicts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Evidence Citations" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Evidence Inventory" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Decision Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,10 +19,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
-  </numFmts>
-  <fonts count="14">
+  <numFmts count="0"/>
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,10 +97,6 @@
       <b val="1"/>
       <color rgb="00A17321"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="000B362C"/>
     </font>
   </fonts>
   <fills count="5">
@@ -199,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -229,11 +222,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1344,838 +1332,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="15" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
-      <c r="C1" s="15" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="D1" s="15" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="E1" s="15" t="inlineStr">
-        <is>
-          <t>Input tokens</t>
-        </is>
-      </c>
-      <c r="F1" s="15" t="inlineStr">
-        <is>
-          <t>Cache read</t>
-        </is>
-      </c>
-      <c r="G1" s="15" t="inlineStr">
-        <is>
-          <t>Output tokens</t>
-        </is>
-      </c>
-      <c r="H1" s="15" t="inlineStr">
-        <is>
-          <t>Cost USD</t>
-        </is>
-      </c>
-      <c r="I1" s="15" t="inlineStr">
-        <is>
-          <t>Latency (ms)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:48:14.126718Z</t>
-        </is>
-      </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
-        </is>
-      </c>
-      <c r="D2" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E2" s="16" t="n">
-        <v>6675</v>
-      </c>
-      <c r="F2" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="16" t="n">
-        <v>1787</v>
-      </c>
-      <c r="H2" s="19" t="n">
-        <v>0.23415</v>
-      </c>
-      <c r="I2" s="16" t="n">
-        <v>25332</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:48:39.485414Z</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E3" s="16" t="n">
-        <v>7348</v>
-      </c>
-      <c r="F3" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="16" t="n">
-        <v>1988</v>
-      </c>
-      <c r="H3" s="19" t="n">
-        <v>0.25932</v>
-      </c>
-      <c r="I3" s="16" t="n">
-        <v>25349</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:00.506620Z</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>7300</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>1515</v>
-      </c>
-      <c r="H4" s="19" t="n">
-        <v>0.223125</v>
-      </c>
-      <c r="I4" s="16" t="n">
-        <v>21014</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:13.305737Z</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-1</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>6270</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>1005</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.119934</v>
-      </c>
-      <c r="I5" s="16" t="n">
-        <v>12795</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:26.208418Z</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-1</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>6246</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>1092</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.126099</v>
-      </c>
-      <c r="I6" s="16" t="n">
-        <v>12900</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:45.900071Z</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-1</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>8041</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>1578</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.189474</v>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>19689</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:10.052239Z</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-31-38 feat use Node.js timers by default · denoland_deno@12cde71.png</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>7264</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>1616</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>0.23016</v>
-      </c>
-      <c r="I8" s="16" t="n">
-        <v>24142</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:31.032351Z</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>7295</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>1504</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.222225</v>
-      </c>
-      <c r="I9" s="16" t="n">
-        <v>20969</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:44.382655Z</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-2</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>4057</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>1067</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>0.091389</v>
-      </c>
-      <c r="I10" s="16" t="n">
-        <v>13346</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:57.753305Z</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-2</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>4033</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>1108</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0.09410399999999999</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>13368</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:51:17.209066Z</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-2</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>5828</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>1487</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>0.149454</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>19453</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:51:31.339364Z</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:kubernetes-pr-checks.png</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>4703</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>945</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>0.14142</v>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>14122</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:52:34.116483Z</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:kubernetes-pr.png</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>4172</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="16" t="n">
-        <v>4640</v>
-      </c>
-      <c r="H14" s="19" t="n">
-        <v>0.41058</v>
-      </c>
-      <c r="I14" s="16" t="n">
-        <v>62769</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:52:46.504782Z</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-3</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>6582</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>1002</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>0.124389</v>
-      </c>
-      <c r="I15" s="16" t="n">
-        <v>12384</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:53:04.324724Z</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-3</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>6558</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>1257</v>
-      </c>
-      <c r="H16" s="19" t="n">
-        <v>0.143154</v>
-      </c>
-      <c r="I16" s="16" t="n">
-        <v>17817</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:53:22.086254Z</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-3</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>8353</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>1369</v>
-      </c>
-      <c r="H17" s="19" t="n">
-        <v>0.178479</v>
-      </c>
-      <c r="I17" s="16" t="n">
-        <v>17758</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:53:36.065782Z</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:nextjs-pr-checks.png</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>4702</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="16" t="n">
-        <v>924</v>
-      </c>
-      <c r="H18" s="19" t="n">
-        <v>0.13983</v>
-      </c>
-      <c r="I18" s="16" t="n">
-        <v>13972</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:01.769450Z</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:nextjs-pr.png</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>6103</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="16" t="n">
-        <v>1808</v>
-      </c>
-      <c r="H19" s="19" t="n">
-        <v>0.227145</v>
-      </c>
-      <c r="I19" s="16" t="n">
-        <v>25696</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:15.073618Z</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-4</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>3730</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G20" s="16" t="n">
-        <v>989</v>
-      </c>
-      <c r="H20" s="19" t="n">
-        <v>0.080634</v>
-      </c>
-      <c r="I20" s="16" t="n">
-        <v>13300</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:26.858373Z</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-4</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>3706</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <v>902</v>
-      </c>
-      <c r="H21" s="19" t="n">
-        <v>0.073749</v>
-      </c>
-      <c r="I21" s="16" t="n">
-        <v>11782</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:43.961668Z</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-4</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>5501</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G22" s="16" t="n">
-        <v>1265</v>
-      </c>
-      <c r="H22" s="19" t="n">
-        <v>0.127899</v>
-      </c>
-      <c r="I22" s="16" t="n">
-        <v>17098</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E23" s="20">
-        <f>SUM(E2:E22)</f>
-        <v/>
-      </c>
-      <c r="F23" s="20">
-        <f>SUM(F2:F22)</f>
-        <v/>
-      </c>
-      <c r="G23" s="20">
-        <f>SUM(G2:G22)</f>
-        <v/>
-      </c>
-      <c r="H23" s="21">
-        <f>SUM(H2:H22)</f>
-        <v/>
-      </c>
-      <c r="I23" s="20">
-        <f>SUM(I2:I22)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/independent-code-review/claude/sample-2/workpaper.xlsx
+++ b/output/independent-code-review/claude/sample-2/workpaper.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Attribute Verdicts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Evidence Citations" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Evidence Inventory" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Decision Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,8 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="13">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
+  </numFmts>
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +100,10 @@
       <b val="1"/>
       <color rgb="00A17321"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B362C"/>
     </font>
   </fonts>
   <fills count="5">
@@ -192,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -222,6 +229,11 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -642,7 +654,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>claude:claude-opus-4-7</t>
+          <t>claude:claude-opus-4-8</t>
         </is>
       </c>
     </row>
@@ -654,7 +666,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 03:51 UTC</t>
+          <t>03 Jul 2026, 04:18 UTC</t>
         </is>
       </c>
     </row>
@@ -730,7 +742,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Provide additional evidence to close “Testing is performed in accordance with the testing policy”. Specifically: The evidence shows CI ran and completed with Success status, and the PR merged with "33 of 36 checks passed" — but no coverage report is present in the evidence bundle.</t>
+          <t>Provide additional evidence to close “Testing is performed in accordance with the testing policy”. Specifically: The change is a production behavioral change (feat: use Node.</t>
         </is>
       </c>
     </row>
@@ -872,20 +884,19 @@
         </is>
       </c>
       <c r="C2" s="16" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>A pull request (PR #31272) exists for the change and shows an approval by dsherret 20 hours ago, followed by the merge to denoland:main 19 hours ago — approval precedes merge by ~1 hour. The PR footer confirms it was "successfully merged and closed" with merge commit 7ada8d6, indicating the change went to main via the PR rather than by direct commit. Independence of the reviewer is a separate attribute; this attribute only requires that the review occurred before the merge, which the evidence positively demonstrates.</t>
+          <t>A code review record exists: dsherret (a human Member, distinct from author bartlomieju) approved the PR with a green checkmark and "LGTM". The approval occurred "20 hours ago" while the merge into denoland:main happened "19 hours ago" — approval precedes merge, and the merge event footer confirms the change was merged only after approval. The Copilot AI review is not a human independent review and is not relied upon. Relative timestamps ("20 hours ago" vs "19 hours ago") are approximate but consistently show approval-before-merge ordering, supporting SUCCESS for this attribute.</t>
         </is>
       </c>
       <c r="E2" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>Independence of dsherret vs. author bartlomieju is relevant to a separate 'independent reviewer' attribute and is not judged here.
-Copilot AI review noted but not relied upon — this attribute is satisfied by the human approval from dsherret regardless.</t>
+          <t>Copilot AI review — rejected as an independent human review; relied on dsherret's human approval instead.</t>
         </is>
       </c>
     </row>
@@ -905,15 +916,15 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>The PR author/committer is bartlomieju and the approving reviewer is dsherret — a different named human — who approved 20 hours ago, before the merge 19 hours ago. Copilot (AI) is also listed as a reviewer but is not relied on for independence; dsherret's human approval satisfies the 4-eyes principle. No indication that dsherret committed or co-authored the 7 commits, all of which are attributed to bartlomieju.</t>
+          <t>The PR was authored and committed by bartlomieju, and the approving review ("dsherret approved these changes 20 hours ago" with green check and "LGTM") was given by dsherret — a different named human. The approval preceded the merge (approved 20 hours ago; merged 19 hours ago), satisfying the 4-eyes principle. The Copilot AI reviewer entry is a bot and not an independent human review, but it is not being relied upon here since dsherret provides the independent human approval.</t>
         </is>
       </c>
       <c r="E3" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>Copilot AI 'review' considered and rejected as satisfying independence — bots/AI do not qualify as an independent human reviewer, but dsherret's human approval independently satisfies the criterion.</t>
+          <t>Copilot AI reviewer — rejected as a valid independent reviewer because it is a bot, not a human; independence is instead satisfied by dsherret's human approval.</t>
         </is>
       </c>
     </row>
@@ -929,21 +940,19 @@
         </is>
       </c>
       <c r="C4" s="16" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>The evidence shows CI ran and completed with Success status, and the PR merged with "33 of 36 checks passed" — but no coverage report is present in the evidence bundle. I cannot verify the policy's numeric thresholds (line ≥80%, branch ≥70%, function ≥80%, integration ≥60%). Additionally, "33 of 36 checks passed" implies 3 checks did not pass — the disposition of those 3 (skipped vs failed) is not shown, and the policy requires all unit/integration/E2E tests to pass with zero failures. A coverage report screenshot for this PR and a breakdown of the 3 non-passing checks would resolve this to SUCCESS or FAIL.</t>
+          <t>The change is a production behavioral change (feat: use Node.js timers by default, +66/−51 across 19 files), so no documentation-only / dependency-bump / refactor exception applies. CI ran on pull_request and the latest re-run reports "Success" with all test/lint jobs green, which addresses the "tests run in CI and pass" and "results visible in status checks" criteria. However, the merge footer shows only "33 of 36 checks passed" (3 checks not passing, un-itemized) and individual pre-merge commits show red X checks, creating ambiguity about whether all required suites truly passed. Critically, no coverage report is present in the evidence bundle, so the ≥80% line, ≥70% branch, ≥80% function, and 100% critical-path thresholds cannot be verified — a coverage report screenshot for this PR's run would resolve this.</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>Documentation-only — rejected: PR modifies runtime timer behavior across 19 files.
-Dependency bump / behavior-preserving refactor — rejected: PR is labeled feat(BREAKING) and changes default timer implementation, a behavioral change.
-Build/deployment scripts — rejected: change is to application logic, not CI/build config.</t>
+          <t>Documentation-only / dependency bump / refactor-with-no-behavioral-change: rejected — this is a behavioral change to runtime timer defaults (Web API to Node.js APIs) touching 19 files, explicitly a feat/BREAKING change, so no testing-policy exception applies.</t>
         </is>
       </c>
     </row>
@@ -958,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1002,12 +1011,12 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>Reviewers panel / approval event</t>
+          <t>Reviewers side panel + review event: 'dsherret approved these changes 20 hours ago'</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>'dsherret approved these changes 20 hours ago' with green check icon; Copilot also listed but as AI reviewer.</t>
+          <t>dsherret (a Member, human) approved the PR with a green check and left 'LGTM', constituting a code review approval record.</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1033,12 @@
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>Merge event line near footer</t>
+          <t>Merge footer: 'bartlomieju merged commit 7ada8d6 into denoland:main 19 hours ago'</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>'bartlomieju merged commit 7ada8d6 into denoland:main 19 hours ago' — merge occurred 1 hour after the 20-hour-ago approval.</t>
+          <t>Merge to main occurred 19 hours ago, which is after the approval logged at 20 hours ago — approval precedes commit to main.</t>
         </is>
       </c>
     </row>
@@ -1046,19 +1055,19 @@
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>PR header / status badge</t>
+          <t>Reviewers side panel row 'Copilot'</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>PR #31272 exists with 'Merged' badge; header states '7 commits into denoland:main from bartlomieju:node_timers', confirming the change reached main via the PR.</t>
+          <t>Copilot shows a pending/comment icon; it is an AI bot, not a human independent reviewer, so it is not counted as the review of record.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Code Reviews are performed prior to committing a change to the main branch</t>
+          <t>Code Review approvals are performed by independent code reviewers</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
@@ -1068,12 +1077,12 @@
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Footer banner</t>
+          <t>Timeline / approval event</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>'Pull request successfully merged and closed — the branch has been merged.'</t>
+          <t>'dsherret approved these changes 20 hours ago' with a green check and a comment 'Unfortunate, but I think we should do this... LGTM' — a human reviewer approval distinct from the author.</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1099,12 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>Reviewers panel / approval event</t>
+          <t>PR header line</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>dsherret (Member) shown with green check; timeline shows 'dsherret approved these changes 20 hours ago' with LGTM comment.</t>
+          <t>'bartlomieju merged 7 commits into denoland:main from bartlomieju:node_timers' identifies bartlomieju as author/committer/merger — different individual from approver dsherret.</t>
         </is>
       </c>
     </row>
@@ -1112,41 +1121,41 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>PR header and commit list</t>
+          <t>Reviewers side panel</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>Header: 'bartlomieju merged 7 commits into denoland:main from bartlomieju:node_timers 19 hours ago'. All 7 listed commits (3461bd5, 0f39d7d, 762a828, 8866044, 8f0236b, 0dbb629, 12cde71) are attributed to bartlomieju; dsherret does not appear as a committer or co-author.</t>
+          <t>Panel lists 'Copilot' (comment/pending icon, an AI bot — not independent human review) and 'dsherret' (green checkmark, the independent human approver).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>Code Review approvals are performed by independent code reviewers</t>
+          <t>Testing is performed in accordance with the testing policy</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
+          <t>Screenshot 2025-11-14 at 14-31-38 feat use Node.js timers by default · denoland_deno@12cde71.png</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>Merge footer</t>
+          <t>Workflow run header + left jobs panel</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>Merge event occurred 19 hours ago, after dsherret's approval 20 hours ago — approval precedes merge.</t>
+          <t>CI workflow (ci.yml, on: pull_request) latest re-run shows Status 'Success' with all test/lint matrix jobs (macos, windows, linux, aarch64 debug+release) and lint jobs showing green checks; 2 artifacts produced.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Code Review approvals are performed by independent code reviewers</t>
+          <t>Testing is performed in accordance with the testing policy</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
@@ -1156,12 +1165,12 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Reviewers panel — Copilot entry</t>
+          <t>Merge event line under Conversation</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>Copilot listed as reviewer with comment icon (AI review). Not counted toward human independence; dsherret provides the independent human approval.</t>
+          <t>Under the merge event it states '33 of 36 checks passed' — 3 checks did not pass and are not itemized; several pre-merge commits show red X check marks.</t>
         </is>
       </c>
     </row>
@@ -1173,17 +1182,17 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Screenshot 2025-11-14 at 14-31-38 feat use Node.js timers by default · denoland_deno@12cde71.png</t>
+          <t>Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>CI workflow run header and jobs list</t>
+          <t>PR title + diff stat + Files changed tab</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>Workflow 'ci' run #71281 (Latest #2) Status: Success, 39m 22s duration; all matrix build (11), matrix lint (3), and test jobs show green success icons; 4 warnings/1 notice are environmental (pwsh cleanup, macOS runner deprecation) and not test failures. No coverage numbers are visible on this page.</t>
+          <t>PR 'feat: use Node.js timers by default' changes runtime timer behavior (Web API to Node.js APIs), diff '+66 −51' across 19 files changed — a production behavioral change, so testing exceptions do not apply.</t>
         </is>
       </c>
     </row>
@@ -1195,39 +1204,17 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
+          <t>Screenshot 2025-11-14 at 14-31-38 feat use Node.js timers by default · denoland_deno@12cde71.png</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Merge footer line</t>
+          <t>Whole page (absence)</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Merge event states '33 of 36 checks passed' — indicating 3 of 36 checks did not pass (state — skipped, cancelled, or failed — not disclosed on this screen). Checks tab shows 18 but no per-check pass/fail detail is captured.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Testing is performed in accordance with the testing policy</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>PR body and diff indicator</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>Diff is +66 −51 across 19 files touching timer behavior (setTimeout/setInterval switching to Node.js APIs) — not a documentation-only, dependency-bump, or refactor-only change, so no policy exception clearly applies. No coverage report screenshot or link is visible on the PR page.</t>
+          <t>No coverage report (line/branch/function %) is displayed anywhere in the CI summary; coverage thresholds cannot be verified from this evidence.</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1282,12 @@
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>GitHub Actions workflow run summary page · 19 facts extracted · 1 people · 5 ambiguity flag(s)</t>
+          <t>GitHub Actions workflow run summary page · 25 facts extracted · 1 people · 7 ambiguity flag(s)</t>
         </is>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
-          <t>testing-per-policy</t>
+          <t>testing-per-testing-policy, testing-per-testing-policy</t>
         </is>
       </c>
     </row>
@@ -1320,13 +1307,847 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>GitHub Pull Request page · 1 facts extracted · 4 people · 3 ambiguity flag(s)</t>
+          <t>GitHub Pull Request page (Conversation tab) · 27 facts extracted · 4 people · 5 ambiguity flag(s)</t>
         </is>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>code-review-prior-to-merge, code-review-prior-to-merge, code-review-prior-to-merge, code-review-prior-to-merge, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, testing-per-policy, testing-per-policy</t>
-        </is>
+          <t>code-review-before-commit-to-main, code-review-before-commit-to-main, code-review-before-commit-to-main, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, testing-per-testing-policy, testing-per-testing-policy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>Input tokens</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>Cache read</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>Output tokens</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>Cost USD</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>Latency (ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:15:40.084130Z</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>4474</v>
+      </c>
+      <c r="F2" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="16" t="n">
+        <v>1660</v>
+      </c>
+      <c r="H2" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="16" t="n">
+        <v>23603</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:06.122392Z</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>5147</v>
+      </c>
+      <c r="F3" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G3" s="16" t="n">
+        <v>2338</v>
+      </c>
+      <c r="H3" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="16" t="n">
+        <v>26026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:30.394765Z</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>5099</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>1763</v>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="16" t="n">
+        <v>24264</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:44.295721Z</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-1</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>6383</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>1065</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>13897</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:55.782597Z</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-1</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>6355</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>927</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>11484</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:17:11.438826Z</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-1</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>8116</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>1317</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>15655</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:17:34.006071Z</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-31-38 feat use Node.js timers by default · denoland_deno@12cde71.png</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>5063</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>1746</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>22559</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:17:57.834234Z</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>5094</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>1921</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>23819</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:09.107798Z</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-2</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>4233</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>946</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>11269</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:20.213919Z</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-2</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>4205</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>943</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>11102</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:39.404920Z</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-2</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>1616</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>19186</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:52.612761Z</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:kubernetes-pr-checks.png</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>2502</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>963</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>13198</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:19:22.610986Z</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:kubernetes-pr.png</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>1971</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>2247</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <v>29989</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:19:35.659572Z</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-3</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>3818</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>1030</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="16" t="n">
+        <v>13044</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:19:48.832139Z</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-3</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>3790</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>994</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>13169</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:03.784191Z</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-3</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>5551</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>1256</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>14948</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:18.239343Z</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:nextjs-pr-checks.png</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>2501</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>1103</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="16" t="n">
+        <v>14446</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:41.669803Z</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:nextjs-pr.png</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>3902</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>1798</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="16" t="n">
+        <v>23426</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:53.838524Z</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-4</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>3513</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>912</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>12165</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:21:02.663985Z</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-4</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>3485</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>711</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>8821</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:21:19.635538Z</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-4</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>5246</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>1284</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <v>16967</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E23" s="20">
+        <f>SUM(E2:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="20">
+        <f>SUM(F2:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="20">
+        <f>SUM(G2:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="21">
+        <f>SUM(H2:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="20">
+        <f>SUM(I2:I22)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
